--- a/astro-site/public/dl/plan-negocio-parrillero-asador-eventos/plan-financiero-parrillero-asador-eventos.xlsx
+++ b/astro-site/public/dl/plan-negocio-parrillero-asador-eventos/plan-financiero-parrillero-asador-eventos.xlsx
@@ -14,7 +14,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pricing Modelo" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">'Inversion Inicial'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'PyG 3 Anos'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Estacionalidad'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Punto Equilibrio'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Pricing Modelo'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -547,7 +553,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -572,6 +578,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -858,17 +865,18 @@
       </c>
       <c r="B21" s="6">
         <f>SUM(B5:B20)</f>
-        <v/>
+        <v>4356.0</v>
       </c>
       <c r="C21" s="6">
         <f>SUM(C5:C20)</f>
-        <v/>
+        <v>10406.0</v>
       </c>
       <c r="D21" s="6">
         <f>SUM(D5:D20)</f>
-        <v/>
-      </c>
-    </row>
+        <v>21036.0</v>
+      </c>
+    </row>
+    <row r="22"/>
     <row r="23" ht="50" customHeight="1">
       <c r="A23" s="7" t="inlineStr">
         <is>
@@ -882,7 +890,16 @@
     <mergeCell ref="A23:D23"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -890,7 +907,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -916,6 +933,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1076,15 +1094,15 @@
       </c>
       <c r="B12" s="5">
         <f>B5+B7+B9</f>
-        <v/>
+        <v>54000.0</v>
       </c>
       <c r="C12" s="5">
         <f>C5+C7+C9</f>
-        <v/>
+        <v>120000.0</v>
       </c>
       <c r="D12" s="5">
         <f>D5+D7+D9</f>
-        <v/>
+        <v>215000.0</v>
       </c>
       <c r="E12" s="5" t="inlineStr"/>
     </row>
@@ -1215,15 +1233,15 @@
       </c>
       <c r="B20" s="5">
         <f>SUM(B12:B16)</f>
-        <v/>
+        <v>77900.0</v>
       </c>
       <c r="C20" s="5">
         <f>SUM(C12:C16)</f>
-        <v/>
+        <v>175500.0</v>
       </c>
       <c r="D20" s="5">
         <f>SUM(D12:D16)</f>
-        <v/>
+        <v>314800.0</v>
       </c>
       <c r="E20" s="5" t="inlineStr"/>
     </row>
@@ -1235,15 +1253,15 @@
       </c>
       <c r="B21" s="4">
         <f>B10-B17</f>
-        <v/>
+        <v>-4496.0</v>
       </c>
       <c r="C21" s="4">
         <f>C10-C17</f>
-        <v/>
+        <v>-11988.0</v>
       </c>
       <c r="D21" s="4">
         <f>D10-D17</f>
-        <v/>
+        <v>-21976.0</v>
       </c>
       <c r="E21" s="4" t="inlineStr"/>
     </row>
@@ -1255,15 +1273,15 @@
       </c>
       <c r="B22" s="5">
         <f>B18/B10</f>
-        <v/>
+        <v>450.0</v>
       </c>
       <c r="C22" s="5">
         <f>C18/C10</f>
-        <v/>
+        <v>300.0</v>
       </c>
       <c r="D22" s="5">
         <f>D18/D10</f>
-        <v/>
+        <v>270.8333333333333</v>
       </c>
       <c r="E22" s="5" t="inlineStr"/>
     </row>
@@ -1403,15 +1421,15 @@
       </c>
       <c r="B31" s="4">
         <f>SUM(B22:B27)</f>
-        <v/>
+        <v>2780.0</v>
       </c>
       <c r="C31" s="4">
         <f>SUM(C22:C27)</f>
-        <v/>
+        <v>5070.0</v>
       </c>
       <c r="D31" s="4">
         <f>SUM(D22:D27)</f>
-        <v/>
+        <v>6330.833333333333</v>
       </c>
       <c r="E31" s="4" t="inlineStr"/>
     </row>
@@ -1430,15 +1448,15 @@
       </c>
       <c r="B33" s="4">
         <f>B18-B28</f>
-        <v/>
+        <v>300.0</v>
       </c>
       <c r="C33" s="4">
         <f>C18-C28</f>
-        <v/>
+        <v>600.0</v>
       </c>
       <c r="D33" s="4">
         <f>D18-D28</f>
-        <v/>
+        <v>1000.0</v>
       </c>
       <c r="E33" s="4" t="inlineStr"/>
     </row>
@@ -1467,24 +1485,33 @@
       </c>
       <c r="B35" s="4">
         <f>B30-B31</f>
-        <v/>
+        <v>-2180.0</v>
       </c>
       <c r="C35" s="4">
         <f>C30-C31</f>
-        <v/>
+        <v>-4170.0</v>
       </c>
       <c r="D35" s="4">
         <f>D30-D31</f>
-        <v/>
+        <v>-4830.833333333333</v>
       </c>
       <c r="E35" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1492,7 +1519,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1517,6 +1544,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1763,11 +1791,11 @@
       </c>
       <c r="B17" s="14">
         <f>SUM(B5:B16)</f>
-        <v/>
+        <v>1.0</v>
       </c>
       <c r="C17" s="15">
         <f>SUM(C5:C16)</f>
-        <v/>
+        <v>48.0</v>
       </c>
       <c r="D17" s="4" t="inlineStr"/>
     </row>
@@ -1776,7 +1804,16 @@
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1784,7 +1821,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1808,6 +1845,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -1878,7 +1916,7 @@
       </c>
       <c r="B8" s="17">
         <f>B6*B7</f>
-        <v/>
+        <v>1624.0</v>
       </c>
       <c r="C8" s="5" t="inlineStr"/>
     </row>
@@ -1890,7 +1928,7 @@
       </c>
       <c r="B9" s="18">
         <f>B5/B8</f>
-        <v/>
+        <v>5.437192118226601</v>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
@@ -1906,7 +1944,7 @@
       </c>
       <c r="B10" s="17">
         <f>B9/12</f>
-        <v/>
+        <v>0.4530993431855501</v>
       </c>
       <c r="C10" s="5" t="inlineStr"/>
     </row>
@@ -1918,7 +1956,7 @@
       </c>
       <c r="B11" s="18">
         <f>B9*0.7/5</f>
-        <v/>
+        <v>0.7612068965517241</v>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
@@ -1928,10 +1966,19 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A2:C2"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A2:C2"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1939,7 +1986,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1966,6 +2013,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2176,10 +2224,19 @@
     </row>
   </sheetData>
   <mergeCells count="2">
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2187,9 +2244,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -2202,6 +2259,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="36" customHeight="1">
       <c r="A3" s="19" t="inlineStr">
         <is>
@@ -2272,20 +2330,37 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/plan-negocio-parrillero-asador-eventos · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A9"/>
+    <mergeCell ref="A11"/>
+    <mergeCell ref="A3"/>
+    <mergeCell ref="A5"/>
     <mergeCell ref="A8"/>
+    <mergeCell ref="A1"/>
+    <mergeCell ref="A12"/>
+    <mergeCell ref="A4"/>
     <mergeCell ref="A6"/>
-    <mergeCell ref="A9"/>
-    <mergeCell ref="A4"/>
-    <mergeCell ref="A12"/>
-    <mergeCell ref="A3"/>
+    <mergeCell ref="A10"/>
     <mergeCell ref="A7"/>
-    <mergeCell ref="A10"/>
-    <mergeCell ref="A11"/>
-    <mergeCell ref="A5"/>
-    <mergeCell ref="A1"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>